--- a/data/trans_orig/IP31KM11_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM11_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36266</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>34066</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>37114</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>91,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>45487</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>43350</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>97,83%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>93,24%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>41832</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>39327</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>42681</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>98,01%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>92,14%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>43727</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>40472</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>44887</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>96,56%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>89,37%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>99,12%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>159</t>
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>89213</t>
+          <t>78098</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>86290</t>
+          <t>75838</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90839</t>
+          <t>79347</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1169</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3369</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1008</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3145</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3354</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1558</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2566</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>769</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,74 +1063,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>151201</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>144222</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>154550</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>96,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>91,84%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>157938</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>155004</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>144195</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>140338</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>145518</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>176755</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>171143</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>179793</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>97,14%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>94,06%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>523</t>
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>334694</t>
+          <t>295396</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>329578</t>
+          <t>289137</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>338097</t>
+          <t>299101</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5841</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2492</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12820</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8,16%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1361</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4295</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5180</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5204</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2166</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>10816</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>7164</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11681</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>198777</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>195396</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>99,33%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>97,64%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>170977</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>167152</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>172580</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>98,79%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>210936</t>
+          <t>172294</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>207779</t>
+          <t>167509</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174022</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>381914</t>
+          <t>371072</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>377454</t>
+          <t>366683</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>384256</t>
+          <t>373480</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4730</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2095</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5920</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1554</t>
+          <t>2378</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8115</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>283842</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>276484</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>288202</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>97,13%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>94,61%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>98,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>271859</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>268123</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>273692</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>99,12%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>99,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>291427</t>
+          <t>252756</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>273270</t>
+          <t>248989</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>299378</t>
+          <t>254215</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>563286</t>
+          <t>536597</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>542138</t>
+          <t>529010</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>571450</t>
+          <t>541861</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8379</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4019</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15737</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6144</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13572</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31729</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>15980</t>
+          <t>10961</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7816</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37128</t>
+          <t>18548</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>670086</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>662166</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>676812</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>96,41%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>98,54%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>904</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>646262</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>640876</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>649796</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>98,12%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>722845</t>
+          <t>611077</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>699061</t>
+          <t>605353</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>731853</t>
+          <t>614642</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1369107</t>
+          <t>1281162</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1347114</t>
+          <t>1271295</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1379103</t>
+          <t>1288578</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>16738</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>10012</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>24658</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>6872</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>3338</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>12258</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21888</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12880</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45672</t>
+          <t>12855</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>28760</t>
+          <t>23869</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18764</t>
+          <t>16453</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50753</t>
+          <t>33736</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
